--- a/business_forms/038_listing_concierge_form--business_forms.xlsx
+++ b/business_forms/038_listing_concierge_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,19 +520,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>snake_case_string</t>
+          <t>property_address</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>&lt;text without colons&gt;</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>&lt;text or null&gt;</t>
-        </is>
-      </c>
+          <t>What is the property address?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -552,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>What is the contact info?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -570,35 +566,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>property_details</t>
+          <t>is_property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>property_details</t>
+          <t>Is the property Yes/No?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_info_2_property_details</t>
+          <t>property_details_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_info_2_property_details</t>
+          <t>What type of property details is this?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_info_2_property_type</t>
+          <t>property_details_type_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact_info_2_property_type</t>
+          <t>Property Details Type 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype</t>
+          <t>property_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype</t>
+          <t>What is the property status?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list</t>
+          <t>property_status_list</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list</t>
+          <t>What is the status list of this property?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status</t>
+          <t>property_subtype_list</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status</t>
+          <t>What is the subtype list?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list</t>
+          <t>property_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list</t>
+          <t>What is the status date?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_info_2_property_type_list</t>
+          <t>status_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_info_2_property_type_list</t>
+          <t>What status date is this property?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list</t>
+          <t>property_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list</t>
+          <t>What is the status time for this property?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list</t>
+          <t>status_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list</t>
+          <t>What status time is this property?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_info_2_property_address</t>
+          <t>property_price</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_info_2_property_address</t>
+          <t>What is the property price range?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_info_2_property_price_range</t>
+          <t>property_price_from</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>contact_info_2_property_price_range</t>
+          <t>From what price range is the property priced?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -846,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact_info_2_property_price_range_from</t>
+          <t>property_price_to</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>contact_info_2_property_price_range_from</t>
+          <t>What price range is the property priced?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>contact_info_2_property_price_range_to</t>
+          <t>minimalist_form_fields_0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>contact_info_2_property_price_range_to</t>
+          <t>Is this property yes or no?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_date</t>
+          <t>minimalist_form_fields_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_date</t>
+          <t>Minimalist Form Fields 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -910,205 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_time</t>
+          <t>minimalist_form_fields_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_time</t>
+          <t>Minimalist Form Fields 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>contact_info_2_property_status_date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>contact_info_2_property_status_date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>contact_info_2_property_status_time</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>contact_info_2_property_status_time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>contact_info_2_property_status_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>contact_info_2_property_status_time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_0</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_0</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_4</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1125,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1153,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>property_details_choices</t>
+          <t>is_property_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1170,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>property_details_choices</t>
+          <t>is_property_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1187,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_choices</t>
+          <t>property_details_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1204,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_choices</t>
+          <t>property_details_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1221,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list_choices</t>
+          <t>property_details_type_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1238,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list_choices</t>
+          <t>property_details_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1255,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_choices</t>
+          <t>property_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1272,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_choices</t>
+          <t>property_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1289,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list_choices</t>
+          <t>property_status_list_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1306,7 +1118,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list_choices</t>
+          <t>property_status_list_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1323,7 +1135,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contact_info_2_property_type_list_choices</t>
+          <t>property_subtype_list_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1340,7 +1152,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contact_info_2_property_type_list_choices</t>
+          <t>property_subtype_list_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1357,7 +1169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list_choices</t>
+          <t>minimalist_form_fields_0_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1374,7 +1186,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contact_info_2_property_subtype_list_choices</t>
+          <t>minimalist_form_fields_0_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1391,41 +1203,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list_choices</t>
+          <t>minimalist_form_fields_1_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_info_2_property_status_list_choices</t>
+          <t>minimalist_form_fields_1_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>minimalist_form_fields_0_choices</t>
+          <t>minimalist_form_fields_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1442,7 +1254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>minimalist_form_fields_0_choices</t>
+          <t>minimalist_form_fields_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1451,142 +1263,6 @@
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_1_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_1_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_3_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_3_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_4_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>minimalist_form_fields_4_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
